--- a/OUTPUT/direct_P0DN68_Fibrobacter_succinogenes_subsp__succinogenes_S85.xlsx
+++ b/OUTPUT/direct_P0DN68_Fibrobacter_succinogenes_subsp__succinogenes_S85.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1238</v>
+        <v>0.1239504198320672</v>
       </c>
     </row>
   </sheetData>
